--- a/src/recipes.xlsx
+++ b/src/recipes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krose\Desktop\Madplanlaegger\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Z6KVV\source\repos\Madplanlaegger\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0015E5-F16F-4012-9364-5C99815219EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBBFA3E-E711-4F9C-8526-4FE75347EFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37125" yWindow="945" windowWidth="28800" windowHeight="15285" xr2:uid="{1DF9BAFE-AC5C-E845-B4CA-1FB82D7DF7D2}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="10920" activeTab="2" xr2:uid="{1DF9BAFE-AC5C-E845-B4CA-1FB82D7DF7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Retter" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="167">
   <si>
     <t>ID</t>
   </si>
@@ -522,6 +522,21 @@
   </si>
   <si>
     <t>Svinekoteletter</t>
+  </si>
+  <si>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Frugt og grønt</t>
+  </si>
+  <si>
+    <t>Køl og frost</t>
+  </si>
+  <si>
+    <t>Kolonial</t>
+  </si>
+  <si>
+    <t>Brød</t>
   </si>
 </sst>
 </file>
@@ -557,9 +572,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,9 +592,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 Tema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -618,7 +632,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -724,7 +738,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -866,7 +880,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -875,13 +889,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788F640D-5B8E-BB42-BF76-8A0950424087}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -892,7 +906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -903,7 +917,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -914,7 +928,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -925,7 +939,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -936,7 +950,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -947,7 +961,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -958,7 +972,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -969,7 +983,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -980,7 +994,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -991,7 +1005,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -1002,7 +1016,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -1013,7 +1027,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>99</v>
       </c>
@@ -1024,7 +1038,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -1035,7 +1049,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -1046,7 +1060,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -1057,7 +1071,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -1068,7 +1082,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>132</v>
       </c>
@@ -1079,7 +1093,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>134</v>
       </c>
@@ -1090,7 +1104,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>138</v>
       </c>
@@ -1101,7 +1115,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>139</v>
       </c>
@@ -1112,7 +1126,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -1123,7 +1137,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -1134,7 +1148,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>147</v>
       </c>
@@ -1145,7 +1159,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>149</v>
       </c>
@@ -1156,7 +1170,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>154</v>
       </c>
@@ -1167,7 +1181,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>157</v>
       </c>
@@ -1178,7 +1192,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>160</v>
       </c>
@@ -1191,15 +1205,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1D6F3A-C42A-9249-9195-C7F544F55CEE}">
-  <dimension ref="A1:C109"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D109"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1209,8 +1230,11 @@
       <c r="C1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1220,8 +1244,11 @@
       <c r="C2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1231,8 +1258,11 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1242,8 +1272,11 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1253,8 +1286,11 @@
       <c r="C5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1264,8 +1300,11 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1275,8 +1314,11 @@
       <c r="C7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1286,8 +1328,11 @@
       <c r="C8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1297,8 +1342,11 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1356,11 @@
       <c r="C10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1319,8 +1370,11 @@
       <c r="C11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1330,8 +1384,11 @@
       <c r="C12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1341,8 +1398,11 @@
       <c r="C13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1352,8 +1412,11 @@
       <c r="C14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1363,8 +1426,11 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1374,8 +1440,11 @@
       <c r="C16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1385,8 +1454,11 @@
       <c r="C17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1396,8 +1468,11 @@
       <c r="C18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1407,8 +1482,11 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1418,8 +1496,11 @@
       <c r="C20" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1429,8 +1510,11 @@
       <c r="C21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1440,8 +1524,11 @@
       <c r="C22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1451,8 +1538,11 @@
       <c r="C23" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1462,8 +1552,11 @@
       <c r="C24" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -1473,8 +1566,11 @@
       <c r="C25" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -1484,8 +1580,11 @@
       <c r="C26" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -1495,8 +1594,11 @@
       <c r="C27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -1506,8 +1608,11 @@
       <c r="C28" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -1517,8 +1622,11 @@
       <c r="C29" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -1528,8 +1636,11 @@
       <c r="C30" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -1539,8 +1650,11 @@
       <c r="C31" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -1550,8 +1664,11 @@
       <c r="C32" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1561,8 +1678,11 @@
       <c r="C33" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>51</v>
       </c>
@@ -1572,8 +1692,11 @@
       <c r="C34" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -1583,8 +1706,11 @@
       <c r="C35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -1594,8 +1720,11 @@
       <c r="C36" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -1605,8 +1734,11 @@
       <c r="C37" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -1616,8 +1748,11 @@
       <c r="C38" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -1627,8 +1762,11 @@
       <c r="C39" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -1638,8 +1776,11 @@
       <c r="C40" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -1649,8 +1790,11 @@
       <c r="C41" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -1660,8 +1804,11 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>62</v>
       </c>
@@ -1671,8 +1818,11 @@
       <c r="C43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>63</v>
       </c>
@@ -1682,8 +1832,11 @@
       <c r="C44" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>64</v>
       </c>
@@ -1693,8 +1846,11 @@
       <c r="C45" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -1704,8 +1860,11 @@
       <c r="C46" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -1715,8 +1874,11 @@
       <c r="C47" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -1726,8 +1888,11 @@
       <c r="C48" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -1737,8 +1902,11 @@
       <c r="C49" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>70</v>
       </c>
@@ -1748,8 +1916,11 @@
       <c r="C50" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -1759,8 +1930,11 @@
       <c r="C51" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>75</v>
       </c>
@@ -1770,8 +1944,11 @@
       <c r="C52" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>76</v>
       </c>
@@ -1781,8 +1958,11 @@
       <c r="C53" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>77</v>
       </c>
@@ -1792,8 +1972,11 @@
       <c r="C54" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>78</v>
       </c>
@@ -1803,8 +1986,11 @@
       <c r="C55" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>80</v>
       </c>
@@ -1814,8 +2000,11 @@
       <c r="C56" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>81</v>
       </c>
@@ -1825,8 +2014,11 @@
       <c r="C57" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>82</v>
       </c>
@@ -1836,8 +2028,11 @@
       <c r="C58" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -1847,8 +2042,11 @@
       <c r="C59" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -1858,8 +2056,11 @@
       <c r="C60" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -1869,8 +2070,11 @@
       <c r="C61" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -1880,8 +2084,11 @@
       <c r="C62" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>90</v>
       </c>
@@ -1891,8 +2098,11 @@
       <c r="C63" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -1902,8 +2112,11 @@
       <c r="C64" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -1913,8 +2126,11 @@
       <c r="C65" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>95</v>
       </c>
@@ -1924,8 +2140,11 @@
       <c r="C66" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>96</v>
       </c>
@@ -1935,8 +2154,11 @@
       <c r="C67" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>97</v>
       </c>
@@ -1946,8 +2168,11 @@
       <c r="C68" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>98</v>
       </c>
@@ -1957,8 +2182,11 @@
       <c r="C69" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>103</v>
       </c>
@@ -1968,8 +2196,11 @@
       <c r="C70" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>105</v>
       </c>
@@ -1979,8 +2210,11 @@
       <c r="C71" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>106</v>
       </c>
@@ -1990,8 +2224,11 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>107</v>
       </c>
@@ -2001,8 +2238,11 @@
       <c r="C73" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>108</v>
       </c>
@@ -2012,8 +2252,11 @@
       <c r="C74" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>109</v>
       </c>
@@ -2023,8 +2266,11 @@
       <c r="C75" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -2034,8 +2280,11 @@
       <c r="C76" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -2045,8 +2294,11 @@
       <c r="C77" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>113</v>
       </c>
@@ -2056,8 +2308,11 @@
       <c r="C78" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>114</v>
       </c>
@@ -2067,8 +2322,11 @@
       <c r="C79" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>117</v>
       </c>
@@ -2078,8 +2336,11 @@
       <c r="C80" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>118</v>
       </c>
@@ -2089,8 +2350,11 @@
       <c r="C81" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>119</v>
       </c>
@@ -2100,8 +2364,11 @@
       <c r="C82" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>122</v>
       </c>
@@ -2111,8 +2378,11 @@
       <c r="C83" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>123</v>
       </c>
@@ -2122,8 +2392,11 @@
       <c r="C84" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>124</v>
       </c>
@@ -2133,8 +2406,11 @@
       <c r="C85" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>125</v>
       </c>
@@ -2144,8 +2420,11 @@
       <c r="C86" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>126</v>
       </c>
@@ -2155,8 +2434,11 @@
       <c r="C87" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>127</v>
       </c>
@@ -2166,8 +2448,11 @@
       <c r="C88" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>128</v>
       </c>
@@ -2177,8 +2462,11 @@
       <c r="C89" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>129</v>
       </c>
@@ -2188,8 +2476,11 @@
       <c r="C90" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>130</v>
       </c>
@@ -2199,8 +2490,11 @@
       <c r="C91" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>131</v>
       </c>
@@ -2210,8 +2504,11 @@
       <c r="C92" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>133</v>
       </c>
@@ -2221,8 +2518,11 @@
       <c r="C93" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>135</v>
       </c>
@@ -2232,8 +2532,11 @@
       <c r="C94" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>136</v>
       </c>
@@ -2243,8 +2546,11 @@
       <c r="C95" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>137</v>
       </c>
@@ -2254,8 +2560,11 @@
       <c r="C96" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>140</v>
       </c>
@@ -2265,8 +2574,11 @@
       <c r="C97" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>141</v>
       </c>
@@ -2276,8 +2588,11 @@
       <c r="C98" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>144</v>
       </c>
@@ -2287,8 +2602,11 @@
       <c r="C99" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>146</v>
       </c>
@@ -2298,8 +2616,11 @@
       <c r="C100" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>148</v>
       </c>
@@ -2309,8 +2630,11 @@
       <c r="C101" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D101" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>150</v>
       </c>
@@ -2320,8 +2644,11 @@
       <c r="C102" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D102" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>151</v>
       </c>
@@ -2331,8 +2658,11 @@
       <c r="C103" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D103" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>152</v>
       </c>
@@ -2342,8 +2672,11 @@
       <c r="C104" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D104" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>155</v>
       </c>
@@ -2353,8 +2686,11 @@
       <c r="C105" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D105" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>156</v>
       </c>
@@ -2364,8 +2700,11 @@
       <c r="C106" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D106" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>158</v>
       </c>
@@ -2375,8 +2714,11 @@
       <c r="C107" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D107" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>159</v>
       </c>
@@ -2386,8 +2728,11 @@
       <c r="C108" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D108" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>161</v>
       </c>
@@ -2397,23 +2742,29 @@
       <c r="C109" t="s">
         <v>19</v>
       </c>
+      <c r="D109" t="s">
+        <v>164</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46356CDD-C11E-954C-B72D-1CB56AB59220}">
-  <dimension ref="A1:G282"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H282"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2435,8 +2786,11 @@
       <c r="G1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2461,8 +2815,12 @@
         <f>VLOOKUP(D2,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" t="str">
+        <f>VLOOKUP(D2,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2487,8 +2845,12 @@
         <f>VLOOKUP(D3,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" t="str">
+        <f>VLOOKUP(D3,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2513,8 +2875,12 @@
         <f>VLOOKUP(D4,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" t="str">
+        <f>VLOOKUP(D4,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2539,8 +2905,12 @@
         <f>VLOOKUP(D5,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" t="str">
+        <f>VLOOKUP(D5,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2565,8 +2935,12 @@
         <f>VLOOKUP(D6,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" t="str">
+        <f>VLOOKUP(D6,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2591,8 +2965,12 @@
         <f>VLOOKUP(D7,Ingredienser!A:C,3,FALSE)</f>
         <v>dl</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" t="str">
+        <f>VLOOKUP(D7,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2617,8 +2995,12 @@
         <f>VLOOKUP(D8,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" t="str">
+        <f>VLOOKUP(D8,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2643,8 +3025,12 @@
         <f>VLOOKUP(D9,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" t="str">
+        <f>VLOOKUP(D9,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2669,8 +3055,12 @@
         <f>VLOOKUP(D10,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" t="str">
+        <f>VLOOKUP(D10,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2695,8 +3085,12 @@
         <f>VLOOKUP(D11,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" t="str">
+        <f>VLOOKUP(D11,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2721,8 +3115,12 @@
         <f>VLOOKUP(D12,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" t="str">
+        <f>VLOOKUP(D12,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2747,8 +3145,12 @@
         <f>VLOOKUP(D13,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" t="str">
+        <f>VLOOKUP(D13,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2773,8 +3175,12 @@
         <f>VLOOKUP(D14,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" t="str">
+        <f>VLOOKUP(D14,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2799,8 +3205,12 @@
         <f>VLOOKUP(D15,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" t="str">
+        <f>VLOOKUP(D15,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2825,8 +3235,12 @@
         <f>VLOOKUP(D16,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" t="str">
+        <f>VLOOKUP(D16,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2851,8 +3265,12 @@
         <f>VLOOKUP(D17,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" t="str">
+        <f>VLOOKUP(D17,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2877,8 +3295,12 @@
         <f>VLOOKUP(D18,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" t="str">
+        <f>VLOOKUP(D18,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2903,8 +3325,12 @@
         <f>VLOOKUP(D19,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" t="str">
+        <f>VLOOKUP(D19,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2929,8 +3355,12 @@
         <f>VLOOKUP(D20,Ingredienser!A:C,3,FALSE)</f>
         <v>pose(r)</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" t="str">
+        <f>VLOOKUP(D20,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2955,8 +3385,12 @@
         <f>VLOOKUP(D21,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" t="str">
+        <f>VLOOKUP(D21,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2981,8 +3415,12 @@
         <f>VLOOKUP(D22,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" t="str">
+        <f>VLOOKUP(D22,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3007,8 +3445,12 @@
         <f>VLOOKUP(D23,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" t="str">
+        <f>VLOOKUP(D23,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3033,8 +3475,12 @@
         <f>VLOOKUP(D24,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" t="str">
+        <f>VLOOKUP(D24,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3059,8 +3505,12 @@
         <f>VLOOKUP(D25,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" t="str">
+        <f>VLOOKUP(D25,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3085,8 +3535,12 @@
         <f>VLOOKUP(D26,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" t="str">
+        <f>VLOOKUP(D26,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3110,8 +3564,12 @@
         <f>VLOOKUP(D27,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" t="str">
+        <f>VLOOKUP(D27,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3135,8 +3593,12 @@
         <f>VLOOKUP(D28,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" t="str">
+        <f>VLOOKUP(D28,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3160,8 +3622,12 @@
         <f>VLOOKUP(D29,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" t="str">
+        <f>VLOOKUP(D29,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3185,8 +3651,12 @@
         <f>VLOOKUP(D30,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" t="str">
+        <f>VLOOKUP(D30,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3210,8 +3680,12 @@
         <f>VLOOKUP(D31,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" t="str">
+        <f>VLOOKUP(D31,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3235,8 +3709,12 @@
         <f>VLOOKUP(D32,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32" t="str">
+        <f>VLOOKUP(D32,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3260,8 +3738,12 @@
         <f>VLOOKUP(D33,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33" t="str">
+        <f>VLOOKUP(D33,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3285,8 +3767,12 @@
         <f>VLOOKUP(D34,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34" t="str">
+        <f>VLOOKUP(D34,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3310,8 +3796,12 @@
         <f>VLOOKUP(D35,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35" t="str">
+        <f>VLOOKUP(D35,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3335,8 +3825,12 @@
         <f>VLOOKUP(D36,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36" t="str">
+        <f>VLOOKUP(D36,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3360,8 +3854,12 @@
         <f>VLOOKUP(D37,Ingredienser!A:C,3,FALSE)</f>
         <v>tsk</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37" t="str">
+        <f>VLOOKUP(D37,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3385,8 +3883,12 @@
         <f>VLOOKUP(D38,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38" t="str">
+        <f>VLOOKUP(D38,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3410,8 +3912,12 @@
         <f>VLOOKUP(D39,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39" t="str">
+        <f>VLOOKUP(D39,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3435,8 +3941,12 @@
         <f>VLOOKUP(D40,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40" t="str">
+        <f>VLOOKUP(D40,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3460,8 +3970,12 @@
         <f>VLOOKUP(D41,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41" t="str">
+        <f>VLOOKUP(D41,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3485,8 +3999,12 @@
         <f>VLOOKUP(D42,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42" t="str">
+        <f>VLOOKUP(D42,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3510,8 +4028,12 @@
         <f>VLOOKUP(D43,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43" t="str">
+        <f>VLOOKUP(D43,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3535,8 +4057,12 @@
         <f>VLOOKUP(D44,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44" t="str">
+        <f>VLOOKUP(D44,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3560,8 +4086,12 @@
         <f>VLOOKUP(D45,Ingredienser!A:C,3,FALSE)</f>
         <v>pakke</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45" t="str">
+        <f>VLOOKUP(D45,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3585,8 +4115,12 @@
         <f>VLOOKUP(D46,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46" t="str">
+        <f>VLOOKUP(D46,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3610,8 +4144,12 @@
         <f>VLOOKUP(D47,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47" t="str">
+        <f>VLOOKUP(D47,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3635,8 +4173,12 @@
         <f>VLOOKUP(D48,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48" t="str">
+        <f>VLOOKUP(D48,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3660,8 +4202,12 @@
         <f>VLOOKUP(D49,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49" t="str">
+        <f>VLOOKUP(D49,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3685,8 +4231,12 @@
         <f>VLOOKUP(D50,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50" t="str">
+        <f>VLOOKUP(D50,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3710,8 +4260,12 @@
         <f>VLOOKUP(D51,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H51" t="str">
+        <f>VLOOKUP(D51,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3735,8 +4289,12 @@
         <f>VLOOKUP(D52,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52" t="str">
+        <f>VLOOKUP(D52,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3760,8 +4318,12 @@
         <f>VLOOKUP(D53,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53" t="str">
+        <f>VLOOKUP(D53,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3785,8 +4347,12 @@
         <f>VLOOKUP(D54,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54" t="str">
+        <f>VLOOKUP(D54,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3810,8 +4376,12 @@
         <f>VLOOKUP(D55,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55" t="str">
+        <f>VLOOKUP(D55,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3835,8 +4405,12 @@
         <f>VLOOKUP(D56,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56" t="str">
+        <f>VLOOKUP(D56,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3860,8 +4434,12 @@
         <f>VLOOKUP(D57,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H57" t="str">
+        <f>VLOOKUP(D57,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3885,8 +4463,12 @@
         <f>VLOOKUP(D58,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58" t="str">
+        <f>VLOOKUP(D58,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3910,8 +4492,12 @@
         <f>VLOOKUP(D59,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H59" t="str">
+        <f>VLOOKUP(D59,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3935,8 +4521,12 @@
         <f>VLOOKUP(D60,Ingredienser!A:C,3,FALSE)</f>
         <v>pakke</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60" t="str">
+        <f>VLOOKUP(D60,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3960,8 +4550,12 @@
         <f>VLOOKUP(D61,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H61" t="str">
+        <f>VLOOKUP(D61,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3985,8 +4579,12 @@
         <f>VLOOKUP(D62,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H62" t="str">
+        <f>VLOOKUP(D62,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4010,8 +4608,12 @@
         <f>VLOOKUP(D63,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H63" t="str">
+        <f>VLOOKUP(D63,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4035,8 +4637,12 @@
         <f>VLOOKUP(D64,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H64" t="str">
+        <f>VLOOKUP(D64,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4060,8 +4666,12 @@
         <f>VLOOKUP(D65,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H65" t="str">
+        <f>VLOOKUP(D65,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4085,8 +4695,12 @@
         <f>VLOOKUP(D66,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H66" t="str">
+        <f>VLOOKUP(D66,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4110,8 +4724,12 @@
         <f>VLOOKUP(D67,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H67" t="str">
+        <f>VLOOKUP(D67,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4135,8 +4753,12 @@
         <f>VLOOKUP(D68,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H68" t="str">
+        <f>VLOOKUP(D68,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4160,8 +4782,12 @@
         <f>VLOOKUP(D69,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H69" t="str">
+        <f>VLOOKUP(D69,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4185,8 +4811,12 @@
         <f>VLOOKUP(D70,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H70" t="str">
+        <f>VLOOKUP(D70,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4210,8 +4840,12 @@
         <f>VLOOKUP(D71,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H71" t="str">
+        <f>VLOOKUP(D71,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4235,8 +4869,12 @@
         <f>VLOOKUP(D72,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H72" t="str">
+        <f>VLOOKUP(D72,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4249,7 +4887,7 @@
       <c r="D73" t="s">
         <v>68</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73">
         <v>0.5</v>
       </c>
       <c r="F73">
@@ -4260,8 +4898,12 @@
         <f>VLOOKUP(D73,Ingredienser!A:C,3,FALSE)</f>
         <v>pakke</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H73" t="str">
+        <f>VLOOKUP(D73,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4274,7 +4916,7 @@
       <c r="D74" t="s">
         <v>38</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74">
         <v>20</v>
       </c>
       <c r="F74">
@@ -4285,8 +4927,12 @@
         <f>VLOOKUP(D74,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H74" t="str">
+        <f>VLOOKUP(D74,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4299,7 +4945,7 @@
       <c r="D75" t="s">
         <v>69</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
@@ -4310,8 +4956,12 @@
         <f>VLOOKUP(D75,Ingredienser!A:C,3,FALSE)</f>
         <v>akke</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H75" t="str">
+        <f>VLOOKUP(D75,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4324,7 +4974,7 @@
       <c r="D76" t="s">
         <v>70</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76">
         <v>2</v>
       </c>
       <c r="F76">
@@ -4335,8 +4985,12 @@
         <f>VLOOKUP(D76,Ingredienser!A:C,3,FALSE)</f>
         <v>psk</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H76" t="str">
+        <f>VLOOKUP(D76,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4349,7 +5003,7 @@
       <c r="D77" t="s">
         <v>12</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77">
         <v>300</v>
       </c>
       <c r="F77">
@@ -4360,8 +5014,12 @@
         <f>VLOOKUP(D77,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H77" t="str">
+        <f>VLOOKUP(D77,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4374,7 +5032,7 @@
       <c r="D78" t="s">
         <v>58</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78">
         <v>1</v>
       </c>
       <c r="F78">
@@ -4385,8 +5043,12 @@
         <f>VLOOKUP(D78,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H78" t="str">
+        <f>VLOOKUP(D78,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4399,7 +5061,7 @@
       <c r="D79" t="s">
         <v>71</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79">
         <v>40</v>
       </c>
       <c r="F79">
@@ -4410,8 +5072,12 @@
         <f>VLOOKUP(D79,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H79" t="str">
+        <f>VLOOKUP(D79,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4424,7 +5090,7 @@
       <c r="D80" t="s">
         <v>75</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E80">
         <v>170</v>
       </c>
       <c r="F80">
@@ -4435,8 +5101,12 @@
         <f>VLOOKUP(D80,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H80" t="str">
+        <f>VLOOKUP(D80,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4449,7 +5119,7 @@
       <c r="D81" t="s">
         <v>41</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81">
         <v>8</v>
       </c>
       <c r="F81">
@@ -4460,8 +5130,12 @@
         <f>VLOOKUP(D81,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H81" t="str">
+        <f>VLOOKUP(D81,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4474,7 +5148,7 @@
       <c r="D82" t="s">
         <v>8</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82">
         <v>2</v>
       </c>
       <c r="F82">
@@ -4485,8 +5159,12 @@
         <f>VLOOKUP(D82,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H82" t="str">
+        <f>VLOOKUP(D82,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4499,7 +5177,7 @@
       <c r="D83" t="s">
         <v>12</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83">
         <v>500</v>
       </c>
       <c r="F83">
@@ -4510,8 +5188,12 @@
         <f>VLOOKUP(D83,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H83" t="str">
+        <f>VLOOKUP(D83,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4524,7 +5206,7 @@
       <c r="D84" t="s">
         <v>76</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84">
         <v>120</v>
       </c>
       <c r="F84">
@@ -4535,8 +5217,12 @@
         <f>VLOOKUP(D84,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H84" t="str">
+        <f>VLOOKUP(D84,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4549,7 +5235,7 @@
       <c r="D85" t="s">
         <v>14</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85">
         <v>2</v>
       </c>
       <c r="F85">
@@ -4560,8 +5246,12 @@
         <f>VLOOKUP(D85,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H85" t="str">
+        <f>VLOOKUP(D85,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4574,7 +5264,7 @@
       <c r="D86" t="s">
         <v>10</v>
       </c>
-      <c r="E86" s="1">
+      <c r="E86">
         <v>1</v>
       </c>
       <c r="F86">
@@ -4585,8 +5275,12 @@
         <f>VLOOKUP(D86,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H86" t="str">
+        <f>VLOOKUP(D86,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4599,7 +5293,7 @@
       <c r="D87" t="s">
         <v>77</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87">
         <v>1</v>
       </c>
       <c r="F87">
@@ -4610,8 +5304,12 @@
         <f>VLOOKUP(D87,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H87" t="str">
+        <f>VLOOKUP(D87,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4624,7 +5322,7 @@
       <c r="D88" t="s">
         <v>78</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88">
         <v>1</v>
       </c>
       <c r="F88">
@@ -4635,8 +5333,12 @@
         <f>VLOOKUP(D88,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H88" t="str">
+        <f>VLOOKUP(D88,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4649,7 +5351,7 @@
       <c r="D89" t="s">
         <v>27</v>
       </c>
-      <c r="E89" s="1">
+      <c r="E89">
         <v>80</v>
       </c>
       <c r="F89">
@@ -4660,8 +5362,12 @@
         <f>VLOOKUP(D89,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H89" t="str">
+        <f>VLOOKUP(D89,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4674,7 +5380,7 @@
       <c r="D90" t="s">
         <v>80</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90">
         <v>450</v>
       </c>
       <c r="F90">
@@ -4685,8 +5391,12 @@
         <f>VLOOKUP(D90,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H90" t="str">
+        <f>VLOOKUP(D90,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4699,7 +5409,7 @@
       <c r="D91" t="s">
         <v>36</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91">
         <v>1</v>
       </c>
       <c r="F91">
@@ -4710,8 +5420,12 @@
         <f>VLOOKUP(D91,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H91" t="str">
+        <f>VLOOKUP(D91,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4724,7 +5438,7 @@
       <c r="D92" t="s">
         <v>9</v>
       </c>
-      <c r="E92" s="1">
+      <c r="E92">
         <v>2</v>
       </c>
       <c r="F92">
@@ -4735,8 +5449,12 @@
         <f>VLOOKUP(D92,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H92" t="str">
+        <f>VLOOKUP(D92,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4749,7 +5467,7 @@
       <c r="D93" t="s">
         <v>42</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E93">
         <v>1</v>
       </c>
       <c r="F93">
@@ -4760,8 +5478,12 @@
         <f>VLOOKUP(D93,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H93" t="str">
+        <f>VLOOKUP(D93,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4774,7 +5496,7 @@
       <c r="D94" t="s">
         <v>81</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E94">
         <v>1</v>
       </c>
       <c r="F94">
@@ -4785,8 +5507,12 @@
         <f>VLOOKUP(D94,Ingredienser!A:C,3,FALSE)</f>
         <v>pakke</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H94" t="str">
+        <f>VLOOKUP(D94,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4799,7 +5525,7 @@
       <c r="D95" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="1">
+      <c r="E95">
         <v>1</v>
       </c>
       <c r="F95">
@@ -4810,8 +5536,12 @@
         <f>VLOOKUP(D95,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H95" t="str">
+        <f>VLOOKUP(D95,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4824,7 +5554,7 @@
       <c r="D96" t="s">
         <v>82</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E96">
         <v>4</v>
       </c>
       <c r="F96">
@@ -4835,8 +5565,12 @@
         <f>VLOOKUP(D96,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H96" t="str">
+        <f>VLOOKUP(D96,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4849,7 +5583,7 @@
       <c r="D97" t="s">
         <v>83</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97">
         <v>1</v>
       </c>
       <c r="F97">
@@ -4860,8 +5594,12 @@
         <f>VLOOKUP(D97,Ingredienser!A:C,3,FALSE)</f>
         <v>dåse</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H97" t="str">
+        <f>VLOOKUP(D97,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4874,7 +5612,7 @@
       <c r="D98" t="s">
         <v>57</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98">
         <v>200</v>
       </c>
       <c r="F98">
@@ -4885,8 +5623,12 @@
         <f>VLOOKUP(D98,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H98" t="str">
+        <f>VLOOKUP(D98,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4899,7 +5641,7 @@
       <c r="D99" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99">
         <v>4</v>
       </c>
       <c r="F99">
@@ -4910,8 +5652,12 @@
         <f>VLOOKUP(D99,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H99" t="str">
+        <f>VLOOKUP(D99,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4924,7 +5670,7 @@
       <c r="D100" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100">
         <v>500</v>
       </c>
       <c r="F100">
@@ -4935,8 +5681,12 @@
         <f>VLOOKUP(D100,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H100" t="str">
+        <f>VLOOKUP(D100,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4949,7 +5699,7 @@
       <c r="D101" t="s">
         <v>52</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E101">
         <v>1</v>
       </c>
       <c r="F101">
@@ -4960,8 +5710,12 @@
         <f>VLOOKUP(D101,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H101" t="str">
+        <f>VLOOKUP(D101,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4974,7 +5728,7 @@
       <c r="D102" t="s">
         <v>14</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102">
         <v>1</v>
       </c>
       <c r="F102">
@@ -4985,8 +5739,12 @@
         <f>VLOOKUP(D102,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H102" t="str">
+        <f>VLOOKUP(D102,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4999,7 +5757,7 @@
       <c r="D103" t="s">
         <v>10</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103">
         <v>1</v>
       </c>
       <c r="F103">
@@ -5010,8 +5768,12 @@
         <f>VLOOKUP(D103,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H103" t="str">
+        <f>VLOOKUP(D103,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5024,7 +5786,7 @@
       <c r="D104" t="s">
         <v>35</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E104">
         <v>1</v>
       </c>
       <c r="F104">
@@ -5035,8 +5797,12 @@
         <f>VLOOKUP(D104,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H104" t="str">
+        <f>VLOOKUP(D104,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5049,7 +5815,7 @@
       <c r="D105" t="s">
         <v>87</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105">
         <v>250</v>
       </c>
       <c r="F105">
@@ -5060,8 +5826,12 @@
         <f>VLOOKUP(D105,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H105" t="str">
+        <f>VLOOKUP(D105,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5074,7 +5844,7 @@
       <c r="D106" t="s">
         <v>88</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E106">
         <v>1</v>
       </c>
       <c r="F106">
@@ -5085,8 +5855,12 @@
         <f>VLOOKUP(D106,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H106" t="str">
+        <f>VLOOKUP(D106,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5099,7 +5873,7 @@
       <c r="D107" t="s">
         <v>30</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E107">
         <v>30</v>
       </c>
       <c r="F107">
@@ -5110,8 +5884,12 @@
         <f>VLOOKUP(D107,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H107" t="str">
+        <f>VLOOKUP(D107,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5124,7 +5902,7 @@
       <c r="D108" t="s">
         <v>89</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E108">
         <v>50</v>
       </c>
       <c r="F108">
@@ -5135,8 +5913,12 @@
         <f>VLOOKUP(D108,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H108" t="str">
+        <f>VLOOKUP(D108,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5149,7 +5931,7 @@
       <c r="D109" t="s">
         <v>90</v>
       </c>
-      <c r="E109" s="1">
+      <c r="E109">
         <v>2</v>
       </c>
       <c r="F109">
@@ -5160,8 +5942,12 @@
         <f>VLOOKUP(D109,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H109" t="str">
+        <f>VLOOKUP(D109,Ingredienser!A:D,4,FALSE)</f>
+        <v>Brød</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5174,7 +5960,7 @@
       <c r="D110" t="s">
         <v>28</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E110">
         <v>50</v>
       </c>
       <c r="F110">
@@ -5185,8 +5971,12 @@
         <f>VLOOKUP(D110,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H110" t="str">
+        <f>VLOOKUP(D110,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5199,7 +5989,7 @@
       <c r="D111" t="s">
         <v>80</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E111">
         <v>450</v>
       </c>
       <c r="F111">
@@ -5210,8 +6000,12 @@
         <f>VLOOKUP(D111,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H111" t="str">
+        <f>VLOOKUP(D111,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5224,7 +6018,7 @@
       <c r="D112" t="s">
         <v>67</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E112">
         <v>1</v>
       </c>
       <c r="F112">
@@ -5235,8 +6029,12 @@
         <f>VLOOKUP(D112,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H112" t="str">
+        <f>VLOOKUP(D112,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5249,7 +6047,7 @@
       <c r="D113" t="s">
         <v>35</v>
       </c>
-      <c r="E113" s="1">
+      <c r="E113">
         <v>1</v>
       </c>
       <c r="F113">
@@ -5260,8 +6058,12 @@
         <f>VLOOKUP(D113,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H113" t="str">
+        <f>VLOOKUP(D113,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5274,7 +6076,7 @@
       <c r="D114" t="s">
         <v>92</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114">
         <v>4</v>
       </c>
       <c r="F114">
@@ -5285,8 +6087,12 @@
         <f>VLOOKUP(D114,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H114" t="str">
+        <f>VLOOKUP(D114,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5299,7 +6105,7 @@
       <c r="D115" t="s">
         <v>30</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115">
         <v>30</v>
       </c>
       <c r="F115">
@@ -5310,8 +6116,12 @@
         <f>VLOOKUP(D115,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H115" t="str">
+        <f>VLOOKUP(D115,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5324,7 +6134,7 @@
       <c r="D116" t="s">
         <v>88</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E116">
         <v>1</v>
       </c>
       <c r="F116">
@@ -5335,8 +6145,12 @@
         <f>VLOOKUP(D116,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H116" t="str">
+        <f>VLOOKUP(D116,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5349,7 +6163,7 @@
       <c r="D117" t="s">
         <v>12</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117">
         <v>400</v>
       </c>
       <c r="F117">
@@ -5360,8 +6174,12 @@
         <f>VLOOKUP(D117,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H117" t="str">
+        <f>VLOOKUP(D117,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5374,7 +6192,7 @@
       <c r="D118" t="s">
         <v>93</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E118">
         <v>1</v>
       </c>
       <c r="F118">
@@ -5385,8 +6203,12 @@
         <f>VLOOKUP(D118,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H118" t="str">
+        <f>VLOOKUP(D118,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5399,7 +6221,7 @@
       <c r="D119" t="s">
         <v>52</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119">
         <v>1</v>
       </c>
       <c r="F119">
@@ -5410,8 +6232,12 @@
         <f>VLOOKUP(D119,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H119" t="str">
+        <f>VLOOKUP(D119,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5424,7 +6250,7 @@
       <c r="D120" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E120">
         <v>500</v>
       </c>
       <c r="F120">
@@ -5435,8 +6261,12 @@
         <f>VLOOKUP(D120,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H120" t="str">
+        <f>VLOOKUP(D120,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5449,7 +6279,7 @@
       <c r="D121" t="s">
         <v>95</v>
       </c>
-      <c r="E121" s="1">
+      <c r="E121">
         <v>3</v>
       </c>
       <c r="F121">
@@ -5460,8 +6290,12 @@
         <f>VLOOKUP(D121,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H121" t="str">
+        <f>VLOOKUP(D121,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5474,7 +6308,7 @@
       <c r="D122" t="s">
         <v>50</v>
       </c>
-      <c r="E122" s="1">
+      <c r="E122">
         <v>1</v>
       </c>
       <c r="F122">
@@ -5485,8 +6319,12 @@
         <f>VLOOKUP(D122,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H122" t="str">
+        <f>VLOOKUP(D122,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5499,7 +6337,7 @@
       <c r="D123" t="s">
         <v>96</v>
       </c>
-      <c r="E123" s="1">
+      <c r="E123">
         <v>1</v>
       </c>
       <c r="F123">
@@ -5510,8 +6348,12 @@
         <f>VLOOKUP(D123,Ingredienser!A:C,3,FALSE)</f>
         <v>dl</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H123" t="str">
+        <f>VLOOKUP(D123,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5524,7 +6366,7 @@
       <c r="D124" t="s">
         <v>97</v>
       </c>
-      <c r="E124" s="1">
+      <c r="E124">
         <v>150</v>
       </c>
       <c r="F124">
@@ -5535,8 +6377,12 @@
         <f>VLOOKUP(D124,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H124" t="str">
+        <f>VLOOKUP(D124,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5549,7 +6395,7 @@
       <c r="D125" t="s">
         <v>98</v>
       </c>
-      <c r="E125" s="1">
+      <c r="E125">
         <v>0.5</v>
       </c>
       <c r="F125">
@@ -5560,8 +6406,12 @@
         <f>VLOOKUP(D125,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H125" t="str">
+        <f>VLOOKUP(D125,Ingredienser!A:D,4,FALSE)</f>
+        <v>Brød</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5574,7 +6424,7 @@
       <c r="D126" t="s">
         <v>51</v>
       </c>
-      <c r="E126" s="1">
+      <c r="E126">
         <v>240</v>
       </c>
       <c r="F126">
@@ -5585,8 +6435,12 @@
         <f>VLOOKUP(D126,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H126" t="str">
+        <f>VLOOKUP(D126,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5599,7 +6453,7 @@
       <c r="D127" t="s">
         <v>12</v>
       </c>
-      <c r="E127" s="1">
+      <c r="E127">
         <v>800</v>
       </c>
       <c r="F127">
@@ -5610,8 +6464,12 @@
         <f>VLOOKUP(D127,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H127" t="str">
+        <f>VLOOKUP(D127,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5624,7 +6482,7 @@
       <c r="D128" t="s">
         <v>55</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128">
         <v>4</v>
       </c>
       <c r="F128">
@@ -5635,8 +6493,12 @@
         <f>VLOOKUP(D128,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H128" t="str">
+        <f>VLOOKUP(D128,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5649,7 +6511,7 @@
       <c r="D129" t="s">
         <v>9</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129">
         <v>4</v>
       </c>
       <c r="F129">
@@ -5660,8 +6522,12 @@
         <f>VLOOKUP(D129,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H129" t="str">
+        <f>VLOOKUP(D129,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -5674,7 +6540,7 @@
       <c r="D130" t="s">
         <v>103</v>
       </c>
-      <c r="E130" s="1">
+      <c r="E130">
         <v>150</v>
       </c>
       <c r="F130">
@@ -5685,8 +6551,12 @@
         <f>VLOOKUP(D130,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H130" t="str">
+        <f>VLOOKUP(D130,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -5699,7 +6569,7 @@
       <c r="D131" t="s">
         <v>36</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131">
         <v>5</v>
       </c>
       <c r="F131">
@@ -5710,8 +6580,12 @@
         <f>VLOOKUP(D131,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H131" t="str">
+        <f>VLOOKUP(D131,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5735,8 +6609,12 @@
         <f>VLOOKUP(D132,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H132" t="str">
+        <f>VLOOKUP(D132,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5760,8 +6638,12 @@
         <f>VLOOKUP(D133,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H133" t="str">
+        <f>VLOOKUP(D133,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5785,8 +6667,12 @@
         <f>VLOOKUP(D134,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H134" t="str">
+        <f>VLOOKUP(D134,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5810,8 +6696,12 @@
         <f>VLOOKUP(D135,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H135" t="str">
+        <f>VLOOKUP(D135,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5835,8 +6725,12 @@
         <f>VLOOKUP(D136,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H136" t="str">
+        <f>VLOOKUP(D136,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -5860,8 +6754,12 @@
         <f>VLOOKUP(D137,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H137" t="str">
+        <f>VLOOKUP(D137,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5885,8 +6783,12 @@
         <f>VLOOKUP(D138,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H138" t="str">
+        <f>VLOOKUP(D138,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5910,8 +6812,12 @@
         <f>VLOOKUP(D139,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H139" t="str">
+        <f>VLOOKUP(D139,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -5935,8 +6841,12 @@
         <f>VLOOKUP(D140,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H140" t="str">
+        <f>VLOOKUP(D140,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -5960,8 +6870,12 @@
         <f>VLOOKUP(D141,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H141" t="str">
+        <f>VLOOKUP(D141,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -5985,8 +6899,12 @@
         <f>VLOOKUP(D142,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H142" t="str">
+        <f>VLOOKUP(D142,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6010,8 +6928,12 @@
         <f>VLOOKUP(D143,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H143" t="str">
+        <f>VLOOKUP(D143,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6035,8 +6957,12 @@
         <f>VLOOKUP(D144,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H144" t="str">
+        <f>VLOOKUP(D144,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6060,8 +6986,12 @@
         <f>VLOOKUP(D145,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H145" t="str">
+        <f>VLOOKUP(D145,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6085,8 +7015,12 @@
         <f>VLOOKUP(D146,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H146" t="str">
+        <f>VLOOKUP(D146,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6110,8 +7044,12 @@
         <f>VLOOKUP(D147,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H147" t="str">
+        <f>VLOOKUP(D147,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6135,8 +7073,12 @@
         <f>VLOOKUP(D148,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H148" t="str">
+        <f>VLOOKUP(D148,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -6160,8 +7102,12 @@
         <f>VLOOKUP(D149,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H149" t="str">
+        <f>VLOOKUP(D149,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -6185,8 +7131,12 @@
         <f>VLOOKUP(D150,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H150" t="str">
+        <f>VLOOKUP(D150,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -6210,8 +7160,12 @@
         <f>VLOOKUP(D151,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H151" t="str">
+        <f>VLOOKUP(D151,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -6235,8 +7189,12 @@
         <f>VLOOKUP(D152,Ingredienser!A:C,3,FALSE)</f>
         <v>Dåse</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H152" t="str">
+        <f>VLOOKUP(D152,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -6260,8 +7218,12 @@
         <f>VLOOKUP(D153,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H153" t="str">
+        <f>VLOOKUP(D153,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -6285,8 +7247,12 @@
         <f>VLOOKUP(D154,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H154" t="str">
+        <f>VLOOKUP(D154,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -6310,8 +7276,12 @@
         <f>VLOOKUP(D155,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H155" t="str">
+        <f>VLOOKUP(D155,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -6335,8 +7305,12 @@
         <f>VLOOKUP(D156,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H156" t="str">
+        <f>VLOOKUP(D156,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -6360,8 +7334,12 @@
         <f>VLOOKUP(D157,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H157" t="str">
+        <f>VLOOKUP(D157,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -6385,8 +7363,12 @@
         <f>VLOOKUP(D158,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H158" t="str">
+        <f>VLOOKUP(D158,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -6410,8 +7392,12 @@
         <f>VLOOKUP(D159,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H159" t="str">
+        <f>VLOOKUP(D159,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -6435,8 +7421,12 @@
         <f>VLOOKUP(D160,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H160" t="str">
+        <f>VLOOKUP(D160,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -6460,8 +7450,12 @@
         <f>VLOOKUP(D161,Ingredienser!A:C,3,FALSE)</f>
         <v>dåse</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H161" t="str">
+        <f>VLOOKUP(D161,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -6485,8 +7479,12 @@
         <f>VLOOKUP(D162,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H162" t="str">
+        <f>VLOOKUP(D162,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -6510,8 +7508,12 @@
         <f>VLOOKUP(D163,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H163" t="str">
+        <f>VLOOKUP(D163,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -6535,8 +7537,12 @@
         <f>VLOOKUP(D164,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H164" t="str">
+        <f>VLOOKUP(D164,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -6560,8 +7566,12 @@
         <f>VLOOKUP(D165,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H165" t="str">
+        <f>VLOOKUP(D165,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -6585,8 +7595,12 @@
         <f>VLOOKUP(D166,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H166" t="str">
+        <f>VLOOKUP(D166,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -6610,8 +7624,12 @@
         <f>VLOOKUP(D167,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H167" t="str">
+        <f>VLOOKUP(D167,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6635,8 +7653,12 @@
         <f>VLOOKUP(D168,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H168" t="str">
+        <f>VLOOKUP(D168,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6660,8 +7682,12 @@
         <f>VLOOKUP(D169,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H169" t="str">
+        <f>VLOOKUP(D169,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6685,8 +7711,12 @@
         <f>VLOOKUP(D170,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H170" t="str">
+        <f>VLOOKUP(D170,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6710,8 +7740,12 @@
         <f>VLOOKUP(D171,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H171" t="str">
+        <f>VLOOKUP(D171,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6735,8 +7769,12 @@
         <f>VLOOKUP(D172,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H172" t="str">
+        <f>VLOOKUP(D172,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6760,8 +7798,12 @@
         <f>VLOOKUP(D173,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H173" t="str">
+        <f>VLOOKUP(D173,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6785,8 +7827,12 @@
         <f>VLOOKUP(D174,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H174" t="str">
+        <f>VLOOKUP(D174,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -6810,8 +7856,12 @@
         <f>VLOOKUP(D175,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H175" t="str">
+        <f>VLOOKUP(D175,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -6835,8 +7885,12 @@
         <f>VLOOKUP(D176,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H176" t="str">
+        <f>VLOOKUP(D176,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -6860,8 +7914,12 @@
         <f>VLOOKUP(D177,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H177" t="str">
+        <f>VLOOKUP(D177,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -6885,8 +7943,12 @@
         <f>VLOOKUP(D178,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H178" t="str">
+        <f>VLOOKUP(D178,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6910,8 +7972,12 @@
         <f>VLOOKUP(D179,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H179" t="str">
+        <f>VLOOKUP(D179,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -6935,8 +8001,12 @@
         <f>VLOOKUP(D180,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H180" t="str">
+        <f>VLOOKUP(D180,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -6960,8 +8030,12 @@
         <f>VLOOKUP(D181,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H181" t="str">
+        <f>VLOOKUP(D181,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -6985,8 +8059,12 @@
         <f>VLOOKUP(D182,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H182" t="str">
+        <f>VLOOKUP(D182,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -7010,8 +8088,12 @@
         <f>VLOOKUP(D183,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H183" t="str">
+        <f>VLOOKUP(D183,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -7035,8 +8117,12 @@
         <f>VLOOKUP(D184,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H184" t="str">
+        <f>VLOOKUP(D184,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -7060,8 +8146,12 @@
         <f>VLOOKUP(D185,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H185" t="str">
+        <f>VLOOKUP(D185,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -7085,8 +8175,12 @@
         <f>VLOOKUP(D186,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H186" t="str">
+        <f>VLOOKUP(D186,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -7110,8 +8204,12 @@
         <f>VLOOKUP(D187,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H187" t="str">
+        <f>VLOOKUP(D187,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -7135,8 +8233,12 @@
         <f>VLOOKUP(D188,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H188" t="str">
+        <f>VLOOKUP(D188,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -7160,8 +8262,12 @@
         <f>VLOOKUP(D189,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H189" t="str">
+        <f>VLOOKUP(D189,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -7185,8 +8291,12 @@
         <f>VLOOKUP(D190,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H190" t="str">
+        <f>VLOOKUP(D190,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -7210,8 +8320,12 @@
         <f>VLOOKUP(D191,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H191" t="str">
+        <f>VLOOKUP(D191,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -7235,8 +8349,12 @@
         <f>VLOOKUP(D192,Ingredienser!A:C,3,FALSE)</f>
         <v>pakke</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H192" t="str">
+        <f>VLOOKUP(D192,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -7260,8 +8378,12 @@
         <f>VLOOKUP(D193,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H193" t="str">
+        <f>VLOOKUP(D193,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -7285,8 +8407,12 @@
         <f>VLOOKUP(D194,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H194" t="str">
+        <f>VLOOKUP(D194,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -7310,8 +8436,12 @@
         <f>VLOOKUP(D195,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H195" t="str">
+        <f>VLOOKUP(D195,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -7335,8 +8465,12 @@
         <f>VLOOKUP(D196,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H196" t="str">
+        <f>VLOOKUP(D196,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -7360,8 +8494,12 @@
         <f>VLOOKUP(D197,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H197" t="str">
+        <f>VLOOKUP(D197,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -7385,8 +8523,12 @@
         <f>VLOOKUP(D198,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H198" t="str">
+        <f>VLOOKUP(D198,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -7410,8 +8552,12 @@
         <f>VLOOKUP(D199,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H199" t="str">
+        <f>VLOOKUP(D199,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -7435,8 +8581,12 @@
         <f>VLOOKUP(D200,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H200" t="str">
+        <f>VLOOKUP(D200,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -7460,8 +8610,12 @@
         <f>VLOOKUP(D201,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H201" t="str">
+        <f>VLOOKUP(D201,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -7485,8 +8639,12 @@
         <f>VLOOKUP(D202,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H202" t="str">
+        <f>VLOOKUP(D202,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -7510,8 +8668,12 @@
         <f>VLOOKUP(D203,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H203" t="str">
+        <f>VLOOKUP(D203,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -7535,8 +8697,12 @@
         <f>VLOOKUP(D204,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H204" t="str">
+        <f>VLOOKUP(D204,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -7560,8 +8726,12 @@
         <f>VLOOKUP(D205,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H205" t="str">
+        <f>VLOOKUP(D205,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -7585,8 +8755,12 @@
         <f>VLOOKUP(D206,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H206" t="str">
+        <f>VLOOKUP(D206,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -7610,8 +8784,12 @@
         <f>VLOOKUP(D207,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H207" t="str">
+        <f>VLOOKUP(D207,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -7635,8 +8813,12 @@
         <f>VLOOKUP(D208,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H208" t="str">
+        <f>VLOOKUP(D208,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -7660,8 +8842,12 @@
         <f>VLOOKUP(D209,Ingredienser!A:C,3,FALSE)</f>
         <v>stilke</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H209" t="str">
+        <f>VLOOKUP(D209,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -7685,8 +8871,12 @@
         <f>VLOOKUP(D210,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H210" t="str">
+        <f>VLOOKUP(D210,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -7710,8 +8900,12 @@
         <f>VLOOKUP(D211,Ingredienser!A:C,3,FALSE)</f>
         <v>dåse</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H211" t="str">
+        <f>VLOOKUP(D211,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -7735,8 +8929,12 @@
         <f>VLOOKUP(D212,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H212" t="str">
+        <f>VLOOKUP(D212,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -7760,8 +8958,12 @@
         <f>VLOOKUP(D213,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H213" t="str">
+        <f>VLOOKUP(D213,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -7785,8 +8987,12 @@
         <f>VLOOKUP(D214,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H214" t="str">
+        <f>VLOOKUP(D214,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -7810,8 +9016,12 @@
         <f>VLOOKUP(D215,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H215" t="str">
+        <f>VLOOKUP(D215,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -7835,8 +9045,12 @@
         <f>VLOOKUP(D216,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H216" t="str">
+        <f>VLOOKUP(D216,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -7860,8 +9074,12 @@
         <f>VLOOKUP(D217,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H217" t="str">
+        <f>VLOOKUP(D217,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -7885,8 +9103,12 @@
         <f>VLOOKUP(D218,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H218" t="str">
+        <f>VLOOKUP(D218,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -7910,8 +9132,12 @@
         <f>VLOOKUP(D219,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H219" t="str">
+        <f>VLOOKUP(D219,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7935,8 +9161,12 @@
         <f>VLOOKUP(D220,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H220" t="str">
+        <f>VLOOKUP(D220,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7960,8 +9190,12 @@
         <f>VLOOKUP(D221,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H221" t="str">
+        <f>VLOOKUP(D221,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7985,8 +9219,12 @@
         <f>VLOOKUP(D222,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H222" t="str">
+        <f>VLOOKUP(D222,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -8010,8 +9248,12 @@
         <f>VLOOKUP(D223,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H223" t="str">
+        <f>VLOOKUP(D223,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -8035,8 +9277,12 @@
         <f>VLOOKUP(D224,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H224" t="str">
+        <f>VLOOKUP(D224,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -8060,8 +9306,12 @@
         <f>VLOOKUP(D225,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H225" t="str">
+        <f>VLOOKUP(D225,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -8085,8 +9335,12 @@
         <f>VLOOKUP(D226,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H226" t="str">
+        <f>VLOOKUP(D226,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -8110,8 +9364,12 @@
         <f>VLOOKUP(D227,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H227" t="str">
+        <f>VLOOKUP(D227,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -8135,8 +9393,12 @@
         <f>VLOOKUP(D228,Ingredienser!A:C,3,FALSE)</f>
         <v>dl</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H228" t="str">
+        <f>VLOOKUP(D228,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -8160,8 +9422,12 @@
         <f>VLOOKUP(D229,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H229" t="str">
+        <f>VLOOKUP(D229,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -8185,8 +9451,12 @@
         <f>VLOOKUP(D230,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H230" t="str">
+        <f>VLOOKUP(D230,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -8210,8 +9480,12 @@
         <f>VLOOKUP(D231,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H231" t="str">
+        <f>VLOOKUP(D231,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -8235,8 +9509,12 @@
         <f>VLOOKUP(D232,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H232" t="str">
+        <f>VLOOKUP(D232,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -8260,8 +9538,12 @@
         <f>VLOOKUP(D233,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H233" t="str">
+        <f>VLOOKUP(D233,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -8285,8 +9567,12 @@
         <f>VLOOKUP(D234,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H234" t="str">
+        <f>VLOOKUP(D234,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -8310,8 +9596,12 @@
         <f>VLOOKUP(D235,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H235" t="str">
+        <f>VLOOKUP(D235,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -8335,8 +9625,12 @@
         <f>VLOOKUP(D236,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H236" t="str">
+        <f>VLOOKUP(D236,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -8360,8 +9654,12 @@
         <f>VLOOKUP(D237,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H237" t="str">
+        <f>VLOOKUP(D237,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -8385,8 +9683,12 @@
         <f>VLOOKUP(D238,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H238" t="str">
+        <f>VLOOKUP(D238,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -8410,8 +9712,12 @@
         <f>VLOOKUP(D239,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H239" t="str">
+        <f>VLOOKUP(D239,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -8435,8 +9741,12 @@
         <f>VLOOKUP(D240,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H240" t="str">
+        <f>VLOOKUP(D240,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -8460,8 +9770,12 @@
         <f>VLOOKUP(D241,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H241" t="str">
+        <f>VLOOKUP(D241,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -8485,8 +9799,12 @@
         <f>VLOOKUP(D242,Ingredienser!A:C,3,FALSE)</f>
         <v>dåse</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H242" t="str">
+        <f>VLOOKUP(D242,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -8510,8 +9828,12 @@
         <f>VLOOKUP(D243,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H243" t="str">
+        <f>VLOOKUP(D243,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -8535,8 +9857,12 @@
         <f>VLOOKUP(D244,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H244" t="str">
+        <f>VLOOKUP(D244,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -8560,8 +9886,12 @@
         <f>VLOOKUP(D245,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H245" t="str">
+        <f>VLOOKUP(D245,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -8585,8 +9915,12 @@
         <f>VLOOKUP(D246,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H246" t="str">
+        <f>VLOOKUP(D246,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -8610,8 +9944,12 @@
         <f>VLOOKUP(D247,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H247" t="str">
+        <f>VLOOKUP(D247,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -8635,8 +9973,12 @@
         <f>VLOOKUP(D248,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H248" t="str">
+        <f>VLOOKUP(D248,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -8660,8 +10002,12 @@
         <f>VLOOKUP(D249,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H249" t="str">
+        <f>VLOOKUP(D249,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -8685,8 +10031,12 @@
         <f>VLOOKUP(D250,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H250" t="str">
+        <f>VLOOKUP(D250,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -8710,8 +10060,12 @@
         <f>VLOOKUP(D251,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H251" t="str">
+        <f>VLOOKUP(D251,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -8735,8 +10089,12 @@
         <f>VLOOKUP(D252,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H252" t="str">
+        <f>VLOOKUP(D252,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -8760,8 +10118,12 @@
         <f>VLOOKUP(D253,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H253" t="str">
+        <f>VLOOKUP(D253,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -8785,8 +10147,12 @@
         <f>VLOOKUP(D254,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H254" t="str">
+        <f>VLOOKUP(D254,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -8810,8 +10176,12 @@
         <f>VLOOKUP(D255,Ingredienser!A:C,3,FALSE)</f>
         <v>pose</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H255" t="str">
+        <f>VLOOKUP(D255,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -8835,8 +10205,12 @@
         <f>VLOOKUP(D256,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H256" t="str">
+        <f>VLOOKUP(D256,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -8860,8 +10234,12 @@
         <f>VLOOKUP(D257,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H257" t="str">
+        <f>VLOOKUP(D257,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -8885,8 +10263,12 @@
         <f>VLOOKUP(D258,Ingredienser!A:C,3,FALSE)</f>
         <v>glas</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H258" t="str">
+        <f>VLOOKUP(D258,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -8910,8 +10292,12 @@
         <f>VLOOKUP(D259,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H259" t="str">
+        <f>VLOOKUP(D259,Ingredienser!A:D,4,FALSE)</f>
+        <v>Brød</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -8935,8 +10321,12 @@
         <f>VLOOKUP(D260,Ingredienser!A:C,3,FALSE)</f>
         <v>pakke</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H260" t="str">
+        <f>VLOOKUP(D260,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8960,8 +10350,12 @@
         <f>VLOOKUP(D261,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H261" t="str">
+        <f>VLOOKUP(D261,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -8985,8 +10379,12 @@
         <f>VLOOKUP(D262,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H262" t="str">
+        <f>VLOOKUP(D262,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -9010,8 +10408,12 @@
         <f>VLOOKUP(D263,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H263" t="str">
+        <f>VLOOKUP(D263,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -9035,8 +10437,12 @@
         <f>VLOOKUP(D264,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H264" t="str">
+        <f>VLOOKUP(D264,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -9060,8 +10466,12 @@
         <f>VLOOKUP(D265,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H265" t="str">
+        <f>VLOOKUP(D265,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -9085,8 +10495,12 @@
         <f>VLOOKUP(D266,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H266" t="str">
+        <f>VLOOKUP(D266,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -9110,8 +10524,12 @@
         <f>VLOOKUP(D267,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H267" t="str">
+        <f>VLOOKUP(D267,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -9135,8 +10553,12 @@
         <f>VLOOKUP(D268,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H268" t="str">
+        <f>VLOOKUP(D268,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -9160,8 +10582,12 @@
         <f>VLOOKUP(D269,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H269" t="str">
+        <f>VLOOKUP(D269,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -9185,8 +10611,12 @@
         <f>VLOOKUP(D270,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H270" t="str">
+        <f>VLOOKUP(D270,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -9210,8 +10640,12 @@
         <f>VLOOKUP(D271,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H271" t="str">
+        <f>VLOOKUP(D271,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -9235,8 +10669,12 @@
         <f>VLOOKUP(D272,Ingredienser!A:C,3,FALSE)</f>
         <v>pakke</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H272" t="str">
+        <f>VLOOKUP(D272,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -9260,8 +10698,12 @@
         <f>VLOOKUP(D273,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H273" t="str">
+        <f>VLOOKUP(D273,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -9285,8 +10727,12 @@
         <f>VLOOKUP(D274,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H274" t="str">
+        <f>VLOOKUP(D274,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -9310,8 +10756,12 @@
         <f>VLOOKUP(D275,Ingredienser!A:C,3,FALSE)</f>
         <v>fed</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H275" t="str">
+        <f>VLOOKUP(D275,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -9335,8 +10785,12 @@
         <f>VLOOKUP(D276,Ingredienser!A:C,3,FALSE)</f>
         <v>stk</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H276" t="str">
+        <f>VLOOKUP(D276,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -9360,8 +10814,12 @@
         <f>VLOOKUP(D277,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H277" t="str">
+        <f>VLOOKUP(D277,Ingredienser!A:D,4,FALSE)</f>
+        <v>Frugt og grønt</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -9385,8 +10843,12 @@
         <f>VLOOKUP(D278,Ingredienser!A:C,3,FALSE)</f>
         <v>dåse</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H278" t="str">
+        <f>VLOOKUP(D278,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -9410,8 +10872,12 @@
         <f>VLOOKUP(D279,Ingredienser!A:C,3,FALSE)</f>
         <v>ml</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H279" t="str">
+        <f>VLOOKUP(D279,Ingredienser!A:D,4,FALSE)</f>
+        <v>Køl og frost</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -9435,8 +10901,12 @@
         <f>VLOOKUP(D280,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H280" t="str">
+        <f>VLOOKUP(D280,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -9460,8 +10930,12 @@
         <f>VLOOKUP(D281,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H281" t="str">
+        <f>VLOOKUP(D281,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -9485,8 +10959,15 @@
         <f>VLOOKUP(D282,Ingredienser!A:C,3,FALSE)</f>
         <v>gram</v>
       </c>
+      <c r="H282" t="str">
+        <f>VLOOKUP(D282,Ingredienser!A:D,4,FALSE)</f>
+        <v>Kolonial</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>